--- a/1. RAG/data/4_testing/range_of_k/RAG_eval_k=5.xlsx
+++ b/1. RAG/data/4_testing/range_of_k/RAG_eval_k=5.xlsx
@@ -548,35 +548,35 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>I don't have enough information to answer that.</t>
+          <t>According to the data provided, 2% of gay men in Germany reported experiencing discrimination in the past year when showing their ID or any official document that identifies their sex.</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.7144</v>
+        <v>0.7181</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="I2" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.577</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>61.2</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="3">
@@ -590,7 +590,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Lesbian women in France feel relatively comfortable being open about their identity at work, with 18% stating they are always open, 54% being selectively open, and 28% hiding their LGBT identity.</t>
+          <t>According to the context provided, 18% of lesbian women in France report being always open about their identity at work, while 54% are selectively open, and 28% hide their LGBT identity. This suggests that a majority of lesbian women in France feel somewhat comfortable being open about their identity at work, but a significant portion still choose to hide it.</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
@@ -603,22 +603,22 @@
         <v>0.8</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.6973</v>
+        <v>0.6972</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="I3" s="4" t="b">
         <v>1</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.391</v>
+        <v>0.256</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>0.867</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>17.1</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="4">
@@ -645,7 +645,7 @@
         <v>0.8</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.7064</v>
+        <v>0.6657</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>8</v>
@@ -729,7 +729,7 @@
         <v>0.8</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.5742</v>
+        <v>0.5777</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>8</v>
@@ -813,7 +813,7 @@
         <v>0.8</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.5152</v>
+        <v>0.51</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>8</v>
@@ -855,7 +855,7 @@
         <v>0.8</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.6084000000000001</v>
+        <v>0.3295</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>8</v>
@@ -864,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0.182</v>
@@ -941,7 +941,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c2a_b_answer_by_Germany.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E2" s="2" t="b">
@@ -949,7 +949,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Question c2a_b — In the last 12 months, in the country where you live, have you personally felt discriminated against or harassed because of being perceived as Gay? | Germany responses (Transgender): Yes: 39%, No: 55%, Don`t know: 6%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,13 @@
       <c r="C3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c2a_c_answer_by_Germany.txt</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="inlineStr"/>
       <c r="E3" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Question c2a_c — In the last 12 months, in the country where you live, have you personally felt discriminated against or harassed because of being perceived as Bisexual? | Germany responses (Transgender): Yes: 19%, No: 73%, Don`t know: 8%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -993,7 +989,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c2a_c_answer_by_Germany.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E4" s="2" t="b">
@@ -1001,7 +997,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Question c2a_c — In the last 12 months, in the country where you live, have you personally felt discriminated against or harassed because of being perceived as Bisexual? | Germany responses (Transgender): Yes: 19%, No: 73%, Don`t know: 8%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1017,13 +1013,17 @@
       <c r="C5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
+        </is>
+      </c>
       <c r="E5" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Germany responses (Bisexual men): Always: 4%, Often: 23%, Rarely: 41%, Never: 32%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c8a_e_answer_by_Germany.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E6" s="2" t="b">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Germany responses (Bisexual men): Always: 4%, Often: 23%, Rarely: 41%, Never: 32%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1214,13 +1214,17 @@
       <c r="C13" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
+        </is>
+      </c>
       <c r="E13" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1236,13 +1240,17 @@
       <c r="C14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1268,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_c_answer_by_Poland.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
         </is>
       </c>
       <c r="E15" s="4" t="b">
@@ -1268,7 +1276,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1294,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_c_answer_by_Poland.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
         </is>
       </c>
       <c r="E16" s="2" t="b">
@@ -1294,7 +1302,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1354,11 +1362,7 @@
       <c r="C19" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_DailyLife\b2_i_answer_by_Gay.txt</t>
-        </is>
-      </c>
+      <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="4" t="b">
         <v>1</v>
       </c>
@@ -1432,24 +1436,22 @@
       <c r="C22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -1465,24 +1467,22 @@
       <c r="C23" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
+        </is>
+      </c>
       <c r="E23" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -1498,28 +1498,18 @@
       <c r="C24" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
-        </is>
-      </c>
+      <c r="D24" s="3" t="inlineStr"/>
       <c r="E24" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1527,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
         </is>
       </c>
       <c r="E25" s="4" t="b">
@@ -1545,18 +1535,12 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1558,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
         </is>
       </c>
       <c r="E26" s="2" t="b">
@@ -1582,18 +1566,12 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1587,11 @@
       <c r="C27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Croatia.txt</t>
+        </is>
+      </c>
       <c r="E27" s="4" t="b">
         <v>0</v>
       </c>
@@ -1761,25 +1743,28 @@
       <c r="C32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="3" t="inlineStr"/>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Slovenia.txt</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -1795,25 +1780,28 @@
       <c r="C33" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Slovenia.txt</t>
+        </is>
+      </c>
       <c r="E33" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -1829,29 +1817,24 @@
       <c r="C34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Malta.txt</t>
-        </is>
-      </c>
+      <c r="D34" s="3" t="inlineStr"/>
       <c r="E34" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -1867,29 +1850,24 @@
       <c r="C35" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Malta.txt</t>
-        </is>
-      </c>
+      <c r="D35" s="5" t="inlineStr"/>
       <c r="E35" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1885,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Malta.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Slovenia.txt</t>
         </is>
       </c>
       <c r="E36" s="2" t="b">
@@ -1915,19 +1893,18 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -1949,19 +1926,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1944,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E38" s="2" t="b">
@@ -1987,19 +1952,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -2017,7 +1970,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E39" s="4" t="b">
@@ -2025,19 +1978,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -2055,7 +1996,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E40" s="2" t="b">
@@ -2063,19 +2004,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2022,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E41" s="4" t="b">
@@ -2101,19 +2030,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
